--- a/dev/CodeSystem-mii-cs-pro-score-catalogue.xlsx
+++ b/dev/CodeSystem-mii-cs-pro-score-catalogue.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026.2.0</t>
+    <t>2026.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T08:53:17+00:00</t>
+    <t>2026-06-14T20:00:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/CodeSystem-mii-cs-pro-score-catalogue.xlsx
+++ b/dev/CodeSystem-mii-cs-pro-score-catalogue.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026.4.0</t>
+    <t>2026.4.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-14T20:00:22+00:00</t>
+    <t>2026-06-15T12:52:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/CodeSystem-mii-cs-pro-score-catalogue.xlsx
+++ b/dev/CodeSystem-mii-cs-pro-score-catalogue.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="120">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T12:52:47+00:00</t>
+    <t>2026-07-07T06:23:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -117,7 +117,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>39</t>
+    <t>40</t>
   </si>
   <si>
     <t>Level</t>
@@ -157,6 +157,12 @@
   </si>
   <si>
     <t>PHQ-9 Total Score</t>
+  </si>
+  <si>
+    <t>phq-phq15-total</t>
+  </si>
+  <si>
+    <t>PHQ-15 Total Score</t>
   </si>
   <si>
     <t>bdi-bdi2-total</t>
@@ -672,7 +678,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1157,6 +1163,18 @@
       </c>
       <c r="D40" s="2"/>
     </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="C41" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="D41" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/dev/CodeSystem-mii-cs-pro-score-catalogue.xlsx
+++ b/dev/CodeSystem-mii-cs-pro-score-catalogue.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="122">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026.4.1</t>
+    <t>2026.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-07T06:23:56+00:00</t>
+    <t>2026-07-07T13:30:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -117,7 +117,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>40</t>
+    <t>41</t>
   </si>
   <si>
     <t>Level</t>
@@ -361,6 +361,12 @@
   </si>
   <si>
     <t>DASS-21 Stress DASS-42 Equivalent Score</t>
+  </si>
+  <si>
+    <t>whodas12-simple-sum</t>
+  </si>
+  <si>
+    <t>WHODAS 2.0 12-Item Simple Sum Score (0-48)</t>
   </si>
   <si>
     <t>proctcae-composite-grade</t>
@@ -678,7 +684,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1175,6 +1181,18 @@
       </c>
       <c r="D41" s="2"/>
     </row>
+    <row r="42">
+      <c r="A42" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="C42" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="D42" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/dev/CodeSystem-mii-cs-pro-score-catalogue.xlsx
+++ b/dev/CodeSystem-mii-cs-pro-score-catalogue.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-07T13:30:17+00:00</t>
+    <t>2026-07-07T13:37:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/CodeSystem-mii-cs-pro-score-catalogue.xlsx
+++ b/dev/CodeSystem-mii-cs-pro-score-catalogue.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-07T13:37:50+00:00</t>
+    <t>2026-07-07T13:59:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/CodeSystem-mii-cs-pro-score-catalogue.xlsx
+++ b/dev/CodeSystem-mii-cs-pro-score-catalogue.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026.5.0</t>
+    <t>2026.5.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-07T13:59:08+00:00</t>
+    <t>2026-07-27T21:31:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/CodeSystem-mii-cs-pro-score-catalogue.xlsx
+++ b/dev/CodeSystem-mii-cs-pro-score-catalogue.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="132">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026.5.2</t>
+    <t>2026.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T21:31:58+00:00</t>
+    <t>2026-09-02T06:41:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -117,7 +117,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>41</t>
+    <t>46</t>
   </si>
   <si>
     <t>Level</t>
@@ -379,6 +379,36 @@
   </si>
   <si>
     <t>PRO-CTCAE Average Composite Score (ACS)</t>
+  </si>
+  <si>
+    <t>scoff-total</t>
+  </si>
+  <si>
+    <t>SCOFF Total Score (0-5)</t>
+  </si>
+  <si>
+    <t>wi-7-total</t>
+  </si>
+  <si>
+    <t>Whiteley-7 Total Score (0-7)</t>
+  </si>
+  <si>
+    <t>pc-ptsd-total</t>
+  </si>
+  <si>
+    <t>PC-PTSD Total Score (0-4)</t>
+  </si>
+  <si>
+    <t>ssd-12-total</t>
+  </si>
+  <si>
+    <t>SSD-12 Total Score (0-48)</t>
+  </si>
+  <si>
+    <t>isr-z-mean</t>
+  </si>
+  <si>
+    <t>ISR-Z Skalenwert (Mittelwert 0-4)</t>
   </si>
 </sst>
 </file>
@@ -684,7 +714,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D47"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1193,6 +1223,66 @@
       </c>
       <c r="D42" s="2"/>
     </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="C43" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="D43" s="2"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="C44" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="D44" s="2"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="C45" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="D45" s="2"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="C46" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="D46" s="2"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="C47" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="D47" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/dev/CodeSystem-mii-cs-pro-score-catalogue.xlsx
+++ b/dev/CodeSystem-mii-cs-pro-score-catalogue.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="134">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026.6.0</t>
+    <t>2026.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T06:41:53+00:00</t>
+    <t>2026-09-02T06:41:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -117,7 +117,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>46</t>
+    <t>47</t>
   </si>
   <si>
     <t>Level</t>
@@ -409,6 +409,12 @@
   </si>
   <si>
     <t>ISR-Z Skalenwert (Mittelwert 0-4)</t>
+  </si>
+  <si>
+    <t>phq-gad7-total</t>
+  </si>
+  <si>
+    <t>GAD-7 Total Score (0-21)</t>
   </si>
 </sst>
 </file>
@@ -714,7 +720,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D47"/>
+  <dimension ref="A1:D48"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1283,6 +1289,18 @@
       </c>
       <c r="D47" s="2"/>
     </row>
+    <row r="48">
+      <c r="A48" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="C48" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="D48" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/dev/CodeSystem-mii-cs-pro-score-catalogue.xlsx
+++ b/dev/CodeSystem-mii-cs-pro-score-catalogue.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T06:41:55+00:00</t>
+    <t>2026-09-02T06:47:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/CodeSystem-mii-cs-pro-score-catalogue.xlsx
+++ b/dev/CodeSystem-mii-cs-pro-score-catalogue.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T06:47:03+00:00</t>
+    <t>2026-09-02T07:20:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
